--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/40.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/40.xlsx
@@ -426,13 +426,13 @@
         <v>-8.771721217127006</v>
       </c>
       <c r="E2">
-        <v>-12.92230606535348</v>
+        <v>-13.0161903884805</v>
       </c>
       <c r="F2">
-        <v>-2.858216429582381</v>
+        <v>-3.598785171359167</v>
       </c>
       <c r="G2">
-        <v>-6.207728836844136</v>
+        <v>-6.921561868322893</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.375748544992868</v>
       </c>
       <c r="E3">
-        <v>-13.94045193344602</v>
+        <v>-13.10954940862264</v>
       </c>
       <c r="F3">
-        <v>-2.857564504436378</v>
+        <v>-3.852955626662347</v>
       </c>
       <c r="G3">
-        <v>-6.861807542503845</v>
+        <v>-5.988149490086095</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.95299270533522</v>
       </c>
       <c r="E4">
-        <v>-13.8496379156962</v>
+        <v>-15.14412485315881</v>
       </c>
       <c r="F4">
-        <v>-2.602520949890646</v>
+        <v>-2.975869451801994</v>
       </c>
       <c r="G4">
-        <v>-7.180430562033725</v>
+        <v>-7.368021279808739</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.40435097352652</v>
       </c>
       <c r="E5">
-        <v>-14.02400227888754</v>
+        <v>-14.04577065344241</v>
       </c>
       <c r="F5">
-        <v>-2.533140209701771</v>
+        <v>-3.050922023597838</v>
       </c>
       <c r="G5">
-        <v>-6.531949620354427</v>
+        <v>-6.671650909469346</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.72942605799289</v>
       </c>
       <c r="E6">
-        <v>-15.09173040889007</v>
+        <v>-14.09249997672756</v>
       </c>
       <c r="F6">
-        <v>-2.516914149015734</v>
+        <v>-3.531588007644071</v>
       </c>
       <c r="G6">
-        <v>-6.607256936365244</v>
+        <v>-7.491765988480077</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.91154697808636</v>
       </c>
       <c r="E7">
-        <v>-15.73327479308272</v>
+        <v>-16.44508297997838</v>
       </c>
       <c r="F7">
-        <v>-2.537599311431041</v>
+        <v>-2.893427014405777</v>
       </c>
       <c r="G7">
-        <v>-6.223193234053799</v>
+        <v>-6.530082605287103</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.95668882752099</v>
       </c>
       <c r="E8">
-        <v>-16.10705503767583</v>
+        <v>-17.80012467187156</v>
       </c>
       <c r="F8">
-        <v>-2.192913150023958</v>
+        <v>-2.869368739926271</v>
       </c>
       <c r="G8">
-        <v>-6.687889674967038</v>
+        <v>-7.284829188390577</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.85817209806196</v>
       </c>
       <c r="E9">
-        <v>-16.52079453691262</v>
+        <v>-17.49801205692384</v>
       </c>
       <c r="F9">
-        <v>-2.366456120910454</v>
+        <v>-3.116306719435609</v>
       </c>
       <c r="G9">
-        <v>-6.095360123319392</v>
+        <v>-5.959438801440954</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.63272152912639</v>
       </c>
       <c r="E10">
-        <v>-17.77532221973155</v>
+        <v>-18.21867793897851</v>
       </c>
       <c r="F10">
-        <v>-2.377325957969989</v>
+        <v>-3.142397807521585</v>
       </c>
       <c r="G10">
-        <v>-5.681450429703238</v>
+        <v>-6.396415482620005</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.28273281659127</v>
       </c>
       <c r="E11">
-        <v>-17.74910688370115</v>
+        <v>-19.44620685976371</v>
       </c>
       <c r="F11">
-        <v>-2.130698616236701</v>
+        <v>-2.360771035425041</v>
       </c>
       <c r="G11">
-        <v>-5.35366623957939</v>
+        <v>-6.000368759173468</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.835757277613606</v>
       </c>
       <c r="E12">
-        <v>-18.66466923009793</v>
+        <v>-19.76408762120613</v>
       </c>
       <c r="F12">
-        <v>-1.958558899730547</v>
+        <v>-2.715033124008486</v>
       </c>
       <c r="G12">
-        <v>-3.579762396447709</v>
+        <v>-5.216586646490468</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.310144244248939</v>
       </c>
       <c r="E13">
-        <v>-18.62198836257564</v>
+        <v>-18.82294845361402</v>
       </c>
       <c r="F13">
-        <v>-1.931820028335582</v>
+        <v>-2.562466900863082</v>
       </c>
       <c r="G13">
-        <v>-3.818733762622068</v>
+        <v>-3.98169563137189</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.744828009879868</v>
       </c>
       <c r="E14">
-        <v>-21.0295606257016</v>
+        <v>-20.16750672817945</v>
       </c>
       <c r="F14">
-        <v>-2.023657808814352</v>
+        <v>-2.010258137706667</v>
       </c>
       <c r="G14">
-        <v>-3.067727772096361</v>
+        <v>-4.066672707318389</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.172440580375662</v>
       </c>
       <c r="E15">
-        <v>-20.69511470633911</v>
+        <v>-22.43293019220464</v>
       </c>
       <c r="F15">
-        <v>-1.558148463137141</v>
+        <v>-2.406350295029279</v>
       </c>
       <c r="G15">
-        <v>-3.193930115715724</v>
+        <v>-2.911298815471394</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.622150467912576</v>
       </c>
       <c r="E16">
-        <v>-22.28586799880554</v>
+        <v>-22.23933792837673</v>
       </c>
       <c r="F16">
-        <v>-1.108038467477974</v>
+        <v>-2.379955196106475</v>
       </c>
       <c r="G16">
-        <v>-3.230003865540259</v>
+        <v>-2.35267740741905</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.121750757842721</v>
       </c>
       <c r="E17">
-        <v>-22.47890778880451</v>
+        <v>-21.88411084179304</v>
       </c>
       <c r="F17">
-        <v>-1.351802971467187</v>
+        <v>-1.518416649029266</v>
       </c>
       <c r="G17">
-        <v>-2.2458998954316</v>
+        <v>-2.828132973825708</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.678677616473913</v>
       </c>
       <c r="E18">
-        <v>-22.71653946235702</v>
+        <v>-23.78882323721125</v>
       </c>
       <c r="F18">
-        <v>-0.9034631969478025</v>
+        <v>-1.23147680763874</v>
       </c>
       <c r="G18">
-        <v>-2.174950041651727</v>
+        <v>-1.889378766890135</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.307330664789111</v>
       </c>
       <c r="E19">
-        <v>-24.54901816887888</v>
+        <v>-24.03956484301596</v>
       </c>
       <c r="F19">
-        <v>-0.775955087737083</v>
+        <v>-1.60974664029012</v>
       </c>
       <c r="G19">
-        <v>-0.5974798083977637</v>
+        <v>-0.9708729781978941</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.997099699561585</v>
       </c>
       <c r="E20">
-        <v>-25.13330905619256</v>
+        <v>-25.56978602342186</v>
       </c>
       <c r="F20">
-        <v>-0.1132189187599358</v>
+        <v>-1.390083485885358</v>
       </c>
       <c r="G20">
-        <v>-1.601963445612134</v>
+        <v>-2.336478016580072</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.748217355600364</v>
       </c>
       <c r="E21">
-        <v>-24.68583242559862</v>
+        <v>-24.36186086661587</v>
       </c>
       <c r="F21">
-        <v>-0.241889227436783</v>
+        <v>-0.9698394485667241</v>
       </c>
       <c r="G21">
-        <v>-1.518672917547189</v>
+        <v>-1.667039912800601</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.548752906033281</v>
       </c>
       <c r="E22">
-        <v>-25.55612361734072</v>
+        <v>-23.12280697948115</v>
       </c>
       <c r="F22">
-        <v>0.1080355294256038</v>
+        <v>-0.7211842634313825</v>
       </c>
       <c r="G22">
-        <v>-2.025857896433678</v>
+        <v>-1.404945778296836</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.396275201209717</v>
       </c>
       <c r="E23">
-        <v>-26.11673511406829</v>
+        <v>-25.77983476179364</v>
       </c>
       <c r="F23">
-        <v>0.1286477955094639</v>
+        <v>-0.4152333901466075</v>
       </c>
       <c r="G23">
-        <v>-1.748545456337208</v>
+        <v>-1.801727495372688</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.292932299275743</v>
       </c>
       <c r="E24">
-        <v>-26.48384038797409</v>
+        <v>-25.77561422401849</v>
       </c>
       <c r="F24">
-        <v>0.3128965867097411</v>
+        <v>-0.1156013034103872</v>
       </c>
       <c r="G24">
-        <v>-2.00539948001054</v>
+        <v>-1.063685611228347</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.23473325201544</v>
       </c>
       <c r="E25">
-        <v>-26.78621112594025</v>
+        <v>-25.97903780491706</v>
       </c>
       <c r="F25">
-        <v>0.5562146006688455</v>
+        <v>-0.7742652182353721</v>
       </c>
       <c r="G25">
-        <v>-2.428024098088579</v>
+        <v>-1.210841835726324</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.22732000707514</v>
       </c>
       <c r="E26">
-        <v>-26.22668193450052</v>
+        <v>-26.75981465094954</v>
       </c>
       <c r="F26">
-        <v>0.717643526656802</v>
+        <v>-0.04660492569641074</v>
       </c>
       <c r="G26">
-        <v>-1.804969342273419</v>
+        <v>-1.17422996556604</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.259490987132486</v>
       </c>
       <c r="E27">
-        <v>-27.01429677628458</v>
+        <v>-25.51341557897438</v>
       </c>
       <c r="F27">
-        <v>0.9101113792276558</v>
+        <v>-0.1056965143751135</v>
       </c>
       <c r="G27">
-        <v>-2.453345284862814</v>
+        <v>-1.652700974585828</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.329367899636979</v>
       </c>
       <c r="E28">
-        <v>-25.93726263219629</v>
+        <v>-25.12078329708734</v>
       </c>
       <c r="F28">
-        <v>0.6587524028895767</v>
+        <v>0.4328938886792775</v>
       </c>
       <c r="G28">
-        <v>-3.190967172647545</v>
+        <v>-2.315133670335884</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.421543962127703</v>
       </c>
       <c r="E29">
-        <v>-25.81096802059638</v>
+        <v>-26.07937520350501</v>
       </c>
       <c r="F29">
-        <v>0.7303655932289967</v>
+        <v>-0.522323071245722</v>
       </c>
       <c r="G29">
-        <v>-2.898393771078098</v>
+        <v>-3.221298784743052</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.526805057474106</v>
       </c>
       <c r="E30">
-        <v>-25.24414345753028</v>
+        <v>-26.62336720062442</v>
       </c>
       <c r="F30">
-        <v>0.9262413492949678</v>
+        <v>-0.5161765851169496</v>
       </c>
       <c r="G30">
-        <v>-2.934500333118228</v>
+        <v>-3.728424701641471</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.632627471848474</v>
       </c>
       <c r="E31">
-        <v>-25.77322318974245</v>
+        <v>-25.45718551722114</v>
       </c>
       <c r="F31">
-        <v>1.002557181380081</v>
+        <v>0.1284895773355292</v>
       </c>
       <c r="G31">
-        <v>-2.745597126719436</v>
+        <v>-2.731182720408795</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.722779552581484</v>
       </c>
       <c r="E32">
-        <v>-25.5150820574092</v>
+        <v>-25.01625706004229</v>
       </c>
       <c r="F32">
-        <v>0.5065241536445143</v>
+        <v>0.5106179453491495</v>
       </c>
       <c r="G32">
-        <v>-3.027270310268408</v>
+        <v>-3.294804710117733</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.790860628691368</v>
       </c>
       <c r="E33">
-        <v>-25.61603079998819</v>
+        <v>-25.14489289270417</v>
       </c>
       <c r="F33">
-        <v>0.6417327662316581</v>
+        <v>-0.01515181541211351</v>
       </c>
       <c r="G33">
-        <v>-3.188834378633906</v>
+        <v>-3.415520851289704</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.823331791890771</v>
       </c>
       <c r="E34">
-        <v>-23.79756772052007</v>
+        <v>-23.1654606761594</v>
       </c>
       <c r="F34">
-        <v>0.7204284978650138</v>
+        <v>0.3889622518392085</v>
       </c>
       <c r="G34">
-        <v>-2.983502095886975</v>
+        <v>-3.081574527077218</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.82151117630638</v>
       </c>
       <c r="E35">
-        <v>-24.10669494170567</v>
+        <v>-23.72039799495536</v>
       </c>
       <c r="F35">
-        <v>0.7145802240012493</v>
+        <v>-0.6517621048723672</v>
       </c>
       <c r="G35">
-        <v>-3.077512374786625</v>
+        <v>-3.06117517264215</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.781613414624527</v>
       </c>
       <c r="E36">
-        <v>-23.27364592020264</v>
+        <v>-24.33795958080339</v>
       </c>
       <c r="F36">
-        <v>0.7322410170289348</v>
+        <v>-0.2913386195468995</v>
       </c>
       <c r="G36">
-        <v>-2.61143453959686</v>
+        <v>-2.04221150468595</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.713542684453222</v>
       </c>
       <c r="E37">
-        <v>-24.11459712884905</v>
+        <v>-25.00983115542541</v>
       </c>
       <c r="F37">
-        <v>0.6404835881882364</v>
+        <v>-0.6066608132595452</v>
       </c>
       <c r="G37">
-        <v>-2.685862488229745</v>
+        <v>-2.781099943992627</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.626566586711075</v>
       </c>
       <c r="E38">
-        <v>-22.98078497765259</v>
+        <v>-21.90093865120554</v>
       </c>
       <c r="F38">
-        <v>0.817029390909881</v>
+        <v>-0.3725086846124174</v>
       </c>
       <c r="G38">
-        <v>-2.839390844996163</v>
+        <v>-3.151169236353041</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.531615680145094</v>
       </c>
       <c r="E39">
-        <v>-22.14147307659696</v>
+        <v>-21.60542855136101</v>
       </c>
       <c r="F39">
-        <v>0.3997500805258665</v>
+        <v>-0.4740019155382185</v>
       </c>
       <c r="G39">
-        <v>-2.648512343218586</v>
+        <v>-2.053813904120147</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.444468519746208</v>
       </c>
       <c r="E40">
-        <v>-21.97958465929675</v>
+        <v>-20.60016166334628</v>
       </c>
       <c r="F40">
-        <v>0.7633379293300283</v>
+        <v>0.08269908404357809</v>
       </c>
       <c r="G40">
-        <v>-1.684525542490882</v>
+        <v>-3.45348130351092</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.370205605133424</v>
       </c>
       <c r="E41">
-        <v>-21.18220642755215</v>
+        <v>-20.20452247471814</v>
       </c>
       <c r="F41">
-        <v>0.3027449441884332</v>
+        <v>-0.08016871612304111</v>
       </c>
       <c r="G41">
-        <v>-1.737445083801606</v>
+        <v>-2.907046352330354</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.320404805637454</v>
       </c>
       <c r="E42">
-        <v>-20.72912354613672</v>
+        <v>-19.85602922898386</v>
       </c>
       <c r="F42">
-        <v>0.6193130024748894</v>
+        <v>0.4783803711344011</v>
       </c>
       <c r="G42">
-        <v>-1.91221606894387</v>
+        <v>-2.314201803413001</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.291710866600115</v>
       </c>
       <c r="E43">
-        <v>-19.66511329329449</v>
+        <v>-20.90734164070858</v>
       </c>
       <c r="F43">
-        <v>0.3625066820960007</v>
+        <v>-0.4332255301354128</v>
       </c>
       <c r="G43">
-        <v>-1.424173736635181</v>
+        <v>-2.616864961277741</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.287007134147218</v>
       </c>
       <c r="E44">
-        <v>-20.03998490012345</v>
+        <v>-19.43471359273224</v>
       </c>
       <c r="F44">
-        <v>0.19407556645218</v>
+        <v>-0.06413400830705107</v>
       </c>
       <c r="G44">
-        <v>-1.334616075391697</v>
+        <v>-2.925129164344453</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.298127239784818</v>
       </c>
       <c r="E45">
-        <v>-19.70006405568569</v>
+        <v>-19.01139637096922</v>
       </c>
       <c r="F45">
-        <v>0.3096212219990719</v>
+        <v>-0.5746692641634283</v>
       </c>
       <c r="G45">
-        <v>-1.880437438140648</v>
+        <v>-3.690336281779437</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.318894127274865</v>
       </c>
       <c r="E46">
-        <v>-18.43490804437076</v>
+        <v>-20.1243232000423</v>
       </c>
       <c r="F46">
-        <v>0.6621727318957359</v>
+        <v>-0.4119538835989243</v>
       </c>
       <c r="G46">
-        <v>-1.257779710134181</v>
+        <v>-1.649291785385565</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.341503438740488</v>
       </c>
       <c r="E47">
-        <v>-18.10425245775269</v>
+        <v>-19.05072616772584</v>
       </c>
       <c r="F47">
-        <v>0.4933945303101422</v>
+        <v>-0.2389037913170936</v>
       </c>
       <c r="G47">
-        <v>-1.397641779105512</v>
+        <v>-1.464634479684694</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.352071618081195</v>
       </c>
       <c r="E48">
-        <v>-17.86614076595538</v>
+        <v>-17.83442786247966</v>
       </c>
       <c r="F48">
-        <v>0.2716778531138405</v>
+        <v>0.3715044088252089</v>
       </c>
       <c r="G48">
-        <v>-1.382653159021968</v>
+        <v>-2.476402428761032</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.345455457384001</v>
       </c>
       <c r="E49">
-        <v>-16.8784353001424</v>
+        <v>-17.62954158447663</v>
       </c>
       <c r="F49">
-        <v>0.606874237554452</v>
+        <v>-0.6832052747478308</v>
       </c>
       <c r="G49">
-        <v>-1.369967956473155</v>
+        <v>-1.518626980445357</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.309602714588999</v>
       </c>
       <c r="E50">
-        <v>-16.61198894647909</v>
+        <v>-16.87932740952191</v>
       </c>
       <c r="F50">
-        <v>0.3563651661716452</v>
+        <v>-0.5441820302707954</v>
       </c>
       <c r="G50">
-        <v>-1.402370019372671</v>
+        <v>-3.436920978300402</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.245978984459358</v>
       </c>
       <c r="E51">
-        <v>-16.41128244998513</v>
+        <v>-16.83732581310077</v>
       </c>
       <c r="F51">
-        <v>0.4270754360420138</v>
+        <v>-0.4993880629644121</v>
       </c>
       <c r="G51">
-        <v>-0.7352025209123368</v>
+        <v>-3.087428226339267</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.15101730600996</v>
       </c>
       <c r="E52">
-        <v>-16.41021825859333</v>
+        <v>-15.83737988204505</v>
       </c>
       <c r="F52">
-        <v>0.598602989037499</v>
+        <v>-0.8676942924949199</v>
       </c>
       <c r="G52">
-        <v>-1.121395736015861</v>
+        <v>-1.748135303642277</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.032723094968423</v>
       </c>
       <c r="E53">
-        <v>-13.96844243128743</v>
+        <v>-16.08290468579292</v>
       </c>
       <c r="F53">
-        <v>0.5043505175795684</v>
+        <v>-0.7918812794233063</v>
       </c>
       <c r="G53">
-        <v>-1.60730855553247</v>
+        <v>-2.395037977751481</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.899808315479874</v>
       </c>
       <c r="E54">
-        <v>-14.52741914889823</v>
+        <v>-14.42536093018736</v>
       </c>
       <c r="F54">
-        <v>0.1655515633041818</v>
+        <v>-0.09588781595856452</v>
       </c>
       <c r="G54">
-        <v>-1.740578650390876</v>
+        <v>-1.82038452115969</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.761301345287672</v>
       </c>
       <c r="E55">
-        <v>-13.72137794637695</v>
+        <v>-15.36556723213389</v>
       </c>
       <c r="F55">
-        <v>0.6459085663091704</v>
+        <v>-1.047256180930157</v>
       </c>
       <c r="G55">
-        <v>-1.399308639657709</v>
+        <v>-2.354360674079045</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.634751184777473</v>
       </c>
       <c r="E56">
-        <v>-13.54733963331417</v>
+        <v>-12.69126332148214</v>
       </c>
       <c r="F56">
-        <v>0.255166005673838</v>
+        <v>-0.5603401648298025</v>
       </c>
       <c r="G56">
-        <v>-1.684856945868386</v>
+        <v>-2.780483074339452</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.528394445660111</v>
       </c>
       <c r="E57">
-        <v>-12.81397138166798</v>
+        <v>-13.59759210937728</v>
       </c>
       <c r="F57">
-        <v>0.4731384622094859</v>
+        <v>-0.09840273939346382</v>
       </c>
       <c r="G57">
-        <v>-2.414571089694856</v>
+        <v>-3.167726280341999</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.459270450257434</v>
       </c>
       <c r="E58">
-        <v>-12.63807186578804</v>
+        <v>-13.89639893829941</v>
       </c>
       <c r="F58">
-        <v>0.3838835312926447</v>
+        <v>-0.2374897681605148</v>
       </c>
       <c r="G58">
-        <v>-2.368332115479161</v>
+        <v>-3.090312420090019</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.430923688354949</v>
       </c>
       <c r="E59">
-        <v>-12.09859928572828</v>
+        <v>-13.32353339090708</v>
       </c>
       <c r="F59">
-        <v>0.7002958565073747</v>
+        <v>-0.3300382878708868</v>
       </c>
       <c r="G59">
-        <v>-2.565136503393096</v>
+        <v>-2.566150400854964</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.452279150875866</v>
       </c>
       <c r="E60">
-        <v>-11.45181998558276</v>
+        <v>-13.37712788078786</v>
       </c>
       <c r="F60">
-        <v>0.6120482203523377</v>
+        <v>0.1126462223895858</v>
       </c>
       <c r="G60">
-        <v>-3.074716774017979</v>
+        <v>-3.743508477150238</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.522684071245986</v>
       </c>
       <c r="E61">
-        <v>-11.17795146302088</v>
+        <v>-13.21796560484027</v>
       </c>
       <c r="F61">
-        <v>0.6744830998687393</v>
+        <v>-0.6772037529145484</v>
       </c>
       <c r="G61">
-        <v>-3.124597904164657</v>
+        <v>-3.705725210893232</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.638162765141433</v>
       </c>
       <c r="E62">
-        <v>-11.31658163781769</v>
+        <v>-12.2611443317596</v>
       </c>
       <c r="F62">
-        <v>0.5775798527218503</v>
+        <v>0.08892509344301917</v>
       </c>
       <c r="G62">
-        <v>-2.990687971102159</v>
+        <v>-4.261803672237007</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.796344619629602</v>
       </c>
       <c r="E63">
-        <v>-11.0071057241335</v>
+        <v>-12.19429952693238</v>
       </c>
       <c r="F63">
-        <v>0.3572473774556266</v>
+        <v>-0.6985292433322189</v>
       </c>
       <c r="G63">
-        <v>-3.176982606361192</v>
+        <v>-4.46481941256297</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.98397693164754</v>
       </c>
       <c r="E64">
-        <v>-11.07828880706007</v>
+        <v>-11.98358963135548</v>
       </c>
       <c r="F64">
-        <v>0.1018766177857895</v>
+        <v>-0.7963851129923273</v>
       </c>
       <c r="G64">
-        <v>-3.80199625144734</v>
+        <v>-4.183129822906201</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.198020137181234</v>
       </c>
       <c r="E65">
-        <v>-10.54660973076751</v>
+        <v>-10.96962807324602</v>
       </c>
       <c r="F65">
-        <v>0.5018355941446692</v>
+        <v>-0.753888208493907</v>
       </c>
       <c r="G65">
-        <v>-3.35651136276465</v>
+        <v>-5.461024527782861</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.42346691131676</v>
       </c>
       <c r="E66">
-        <v>-11.36034481062782</v>
+        <v>-10.55750976770397</v>
       </c>
       <c r="F66">
-        <v>0.3123821705526026</v>
+        <v>-0.9072306118957347</v>
       </c>
       <c r="G66">
-        <v>-3.643329501718832</v>
+        <v>-5.131527540004982</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.656232989884676</v>
       </c>
       <c r="E67">
-        <v>-10.44712821376701</v>
+        <v>-13.06186910579587</v>
       </c>
       <c r="F67">
-        <v>-0.09318982332764654</v>
+        <v>-0.9738992772078445</v>
       </c>
       <c r="G67">
-        <v>-3.392919797188249</v>
+        <v>-4.18945601807281</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.885350250668798</v>
       </c>
       <c r="E68">
-        <v>-10.84894424094161</v>
+        <v>-12.25448747496833</v>
       </c>
       <c r="F68">
-        <v>0.1738186699841209</v>
+        <v>-0.9663661040467858</v>
       </c>
       <c r="G68">
-        <v>-3.673661113814338</v>
+        <v>-4.062748366333293</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.105358164290882</v>
       </c>
       <c r="E69">
-        <v>-10.06604354059952</v>
+        <v>-10.71525915976117</v>
       </c>
       <c r="F69">
-        <v>-0.06217077756241625</v>
+        <v>-1.402137888330897</v>
       </c>
       <c r="G69">
-        <v>-3.821916547534729</v>
+        <v>-5.058307080905974</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.314513618854408</v>
       </c>
       <c r="E70">
-        <v>-10.73572333380183</v>
+        <v>-10.34009773059572</v>
       </c>
       <c r="F70">
-        <v>-0.2762151158739889</v>
+        <v>-1.475087235291032</v>
       </c>
       <c r="G70">
-        <v>-3.822513729858548</v>
+        <v>-5.581360047253937</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.505987645163338</v>
       </c>
       <c r="E71">
-        <v>-10.09895648968727</v>
+        <v>-12.6394621073084</v>
       </c>
       <c r="F71">
-        <v>-0.2701464962810797</v>
+        <v>-1.255330475369754</v>
       </c>
       <c r="G71">
-        <v>-4.005185896515955</v>
+        <v>-4.481471611977152</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.685716470181599</v>
       </c>
       <c r="E72">
-        <v>-10.23935729782109</v>
+        <v>-12.43529585667258</v>
       </c>
       <c r="F72">
-        <v>-0.4906247642101961</v>
+        <v>-1.930289205375208</v>
       </c>
       <c r="G72">
-        <v>-3.578873185405099</v>
+        <v>-5.130503798878435</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.84750117716229</v>
       </c>
       <c r="E73">
-        <v>-10.68663014708468</v>
+        <v>-12.28722834204378</v>
       </c>
       <c r="F73">
-        <v>-0.413830964133668</v>
+        <v>-1.268357381146179</v>
       </c>
       <c r="G73">
-        <v>-4.144627969127677</v>
+        <v>-5.272659441719819</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.997063685605173</v>
       </c>
       <c r="E74">
-        <v>-11.51895008427247</v>
+        <v>-10.89682832509871</v>
       </c>
       <c r="F74">
-        <v>-0.3038602212076168</v>
+        <v>-1.107678956025159</v>
       </c>
       <c r="G74">
-        <v>-3.959009265509889</v>
+        <v>-4.600639016573065</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.128589617025604</v>
       </c>
       <c r="E75">
-        <v>-11.74841691918914</v>
+        <v>-11.99858340879487</v>
       </c>
       <c r="F75">
-        <v>-0.4640126330278592</v>
+        <v>-0.8331538569003889</v>
       </c>
       <c r="G75">
-        <v>-3.674937509000963</v>
+        <v>-3.639434691727771</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.24393178784964</v>
       </c>
       <c r="E76">
-        <v>-12.25958200822696</v>
+        <v>-13.82620759118051</v>
       </c>
       <c r="F76">
-        <v>-0.4768407306276123</v>
+        <v>-1.515515706384662</v>
       </c>
       <c r="G76">
-        <v>-3.323918989014686</v>
+        <v>-2.611244228746413</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.341444562017574</v>
       </c>
       <c r="E77">
-        <v>-11.68538961795038</v>
+        <v>-13.43374739130576</v>
       </c>
       <c r="F77">
-        <v>-0.9887303671875669</v>
+        <v>-2.259714354120515</v>
       </c>
       <c r="G77">
-        <v>-3.508064424152283</v>
+        <v>-3.871082371381449</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.41743641103248</v>
       </c>
       <c r="E78">
-        <v>-12.54510229441057</v>
+        <v>-13.25787957474388</v>
       </c>
       <c r="F78">
-        <v>-0.7802501727205985</v>
+        <v>-1.176156775744983</v>
       </c>
       <c r="G78">
-        <v>-2.705969813946022</v>
+        <v>-5.628297921661794</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.476412159844325</v>
       </c>
       <c r="E79">
-        <v>-12.59366564966883</v>
+        <v>-15.55909156885168</v>
       </c>
       <c r="F79">
-        <v>-0.9891892827287178</v>
+        <v>-1.759676998359816</v>
       </c>
       <c r="G79">
-        <v>-2.322765791683152</v>
+        <v>-5.185067232190442</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.512170462423748</v>
       </c>
       <c r="E80">
-        <v>-14.16060369732892</v>
+        <v>-14.91364816853843</v>
       </c>
       <c r="F80">
-        <v>-1.075086840562012</v>
+        <v>-2.197301840523989</v>
       </c>
       <c r="G80">
-        <v>-2.755155325122098</v>
+        <v>-5.532161411191622</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.530677720969473</v>
       </c>
       <c r="E81">
-        <v>-13.94689595195894</v>
+        <v>-15.83243478842867</v>
       </c>
       <c r="F81">
-        <v>-1.197861658433136</v>
+        <v>-2.018557550715315</v>
       </c>
       <c r="G81">
-        <v>-2.426311300434549</v>
+        <v>-4.325469214154912</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.524283645525105</v>
       </c>
       <c r="E82">
-        <v>-15.03515165463823</v>
+        <v>-14.23724359143473</v>
       </c>
       <c r="F82">
-        <v>-1.344408964029799</v>
+        <v>-2.477489659214297</v>
       </c>
       <c r="G82">
-        <v>-2.69339617293023</v>
+        <v>-3.179998048974322</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.494862353333424</v>
       </c>
       <c r="E83">
-        <v>-15.71628395860594</v>
+        <v>-17.59242621150976</v>
       </c>
       <c r="F83">
-        <v>-1.35821867700187</v>
+        <v>-2.788181279145294</v>
       </c>
       <c r="G83">
-        <v>-2.767295844892044</v>
+        <v>-1.819649527530375</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.433953196883308</v>
       </c>
       <c r="E84">
-        <v>-16.70683783456974</v>
+        <v>-17.76825327180558</v>
       </c>
       <c r="F84">
-        <v>-1.663876308226053</v>
+        <v>-2.172076396373939</v>
       </c>
       <c r="G84">
-        <v>-1.89797556737588</v>
+        <v>-2.799507596941112</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.33683465864547</v>
       </c>
       <c r="E85">
-        <v>-17.84272855533572</v>
+        <v>-19.4677533390922</v>
       </c>
       <c r="F85">
-        <v>-1.650605862433205</v>
+        <v>-2.36252551758417</v>
       </c>
       <c r="G85">
-        <v>-0.8138829326862617</v>
+        <v>-2.087387363116385</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.200255855372708</v>
       </c>
       <c r="E86">
-        <v>-18.9688151298751</v>
+        <v>-20.67696911099038</v>
       </c>
       <c r="F86">
-        <v>-1.923440263688862</v>
+        <v>-2.742704737099004</v>
       </c>
       <c r="G86">
-        <v>-1.418894251146035</v>
+        <v>-1.085459797496822</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.017430670330637</v>
       </c>
       <c r="E87">
-        <v>-20.18658066069975</v>
+        <v>-20.12732557830939</v>
       </c>
       <c r="F87">
-        <v>-1.844920974312302</v>
+        <v>-2.553729281498352</v>
       </c>
       <c r="G87">
-        <v>-1.265723547529596</v>
+        <v>-1.958035046799956</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.793582337966733</v>
       </c>
       <c r="E88">
-        <v>-21.43996716806875</v>
+        <v>-22.01683135800985</v>
       </c>
       <c r="F88">
-        <v>-2.134053504218039</v>
+        <v>-2.913059321852125</v>
       </c>
       <c r="G88">
-        <v>-1.404863747757849</v>
+        <v>-2.336238487406232</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.526826115948137</v>
       </c>
       <c r="E89">
-        <v>-22.26214785195336</v>
+        <v>-22.45601182422173</v>
       </c>
       <c r="F89">
-        <v>-2.271709114113052</v>
+        <v>-2.924626644264817</v>
       </c>
       <c r="G89">
-        <v>-0.697205975253967</v>
+        <v>-0.860302374087726</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.23052279139904</v>
       </c>
       <c r="E90">
-        <v>-23.97816779241997</v>
+        <v>-25.30991501401769</v>
       </c>
       <c r="F90">
-        <v>-2.272792618675914</v>
+        <v>-3.457531961833795</v>
       </c>
       <c r="G90">
-        <v>-1.078241110066044</v>
+        <v>-2.758964823352613</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.909436917523334</v>
       </c>
       <c r="E91">
-        <v>-26.08028089830654</v>
+        <v>-27.35036841781582</v>
       </c>
       <c r="F91">
-        <v>-2.564008492599692</v>
+        <v>-2.798032224299385</v>
       </c>
       <c r="G91">
-        <v>-0.7080372876216939</v>
+        <v>-1.419156748870791</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-5.579644399907431</v>
       </c>
       <c r="E92">
-        <v>-27.99096635094087</v>
+        <v>-28.61699618318324</v>
       </c>
       <c r="F92">
-        <v>-3.012542105091331</v>
+        <v>-2.878024350918122</v>
       </c>
       <c r="G92">
-        <v>-0.8130002840867711</v>
+        <v>-2.169887116785504</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.253919895670257</v>
       </c>
       <c r="E93">
-        <v>-30.89917273679981</v>
+        <v>-30.75926779656984</v>
       </c>
       <c r="F93">
-        <v>-2.935701916440246</v>
+        <v>-2.466514619494606</v>
       </c>
       <c r="G93">
-        <v>-0.88125625496634</v>
+        <v>-2.208667874396581</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.943954872369488</v>
       </c>
       <c r="E94">
-        <v>-31.92672877388029</v>
+        <v>-33.19497999717946</v>
       </c>
       <c r="F94">
-        <v>-3.015190395678081</v>
+        <v>-3.221897883903059</v>
       </c>
       <c r="G94">
-        <v>-0.8027136544979118</v>
+        <v>-2.855813358901184</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.66637952650576</v>
       </c>
       <c r="E95">
-        <v>-34.77543327551545</v>
+        <v>-34.07307374963678</v>
       </c>
       <c r="F95">
-        <v>-3.418678217172887</v>
+        <v>-3.559634871168056</v>
       </c>
       <c r="G95">
-        <v>-0.9183898393545759</v>
+        <v>-2.318208174937083</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.426655838895114</v>
       </c>
       <c r="E96">
-        <v>-36.50039015943619</v>
+        <v>-38.09631949769338</v>
       </c>
       <c r="F96">
-        <v>-3.106481453671004</v>
+        <v>-3.746457399888832</v>
       </c>
       <c r="G96">
-        <v>-1.961887200910744</v>
+        <v>-2.550909126711343</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.236379812216258</v>
       </c>
       <c r="E97">
-        <v>-38.60316668676488</v>
+        <v>-40.2633414857689</v>
       </c>
       <c r="F97">
-        <v>-3.585301835143799</v>
+        <v>-4.377207818341682</v>
       </c>
       <c r="G97">
-        <v>-1.570273407791017</v>
+        <v>-3.691944080343565</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.092653208110335</v>
       </c>
       <c r="E98">
-        <v>-41.35015260523974</v>
+        <v>-41.06639389544511</v>
       </c>
       <c r="F98">
-        <v>-3.61430877648763</v>
+        <v>-4.084582063098339</v>
       </c>
       <c r="G98">
-        <v>-1.920799744543377</v>
+        <v>-2.684152971797274</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.996250140322982</v>
       </c>
       <c r="E99">
-        <v>-43.91664939942789</v>
+        <v>-42.48652560848754</v>
       </c>
       <c r="F99">
-        <v>-3.652932235010559</v>
+        <v>-4.464656079953017</v>
       </c>
       <c r="G99">
-        <v>-2.100738653641766</v>
+        <v>-3.657648752604248</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.939858824568232</v>
       </c>
       <c r="E100">
-        <v>-45.4864901989269</v>
+        <v>-45.91020819063959</v>
       </c>
       <c r="F100">
-        <v>-3.595221534792323</v>
+        <v>-3.761286833133748</v>
       </c>
       <c r="G100">
-        <v>-2.548179150373885</v>
+        <v>-2.509342611996297</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.90951521598993</v>
       </c>
       <c r="E101">
-        <v>-47.76760482538867</v>
+        <v>-48.13470330658346</v>
       </c>
       <c r="F101">
-        <v>-4.096655517994142</v>
+        <v>-4.899299627834515</v>
       </c>
       <c r="G101">
-        <v>-2.858763177083125</v>
+        <v>-3.391525278025485</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.899464160965573</v>
       </c>
       <c r="E102">
-        <v>-50.46817728164041</v>
+        <v>-51.21085041525386</v>
       </c>
       <c r="F102">
-        <v>-3.680458055438184</v>
+        <v>-4.910049351620644</v>
       </c>
       <c r="G102">
-        <v>-3.181894595035681</v>
+        <v>-3.533884356603553</v>
       </c>
     </row>
   </sheetData>
